--- a/data/trans_camb/IP16A09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 2,7</t>
+          <t>-29,08; 2,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,74; 3,74</t>
+          <t>-24,87; 2,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 0,0</t>
+          <t>-24,88; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 0,0</t>
+          <t>-23,08; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 0,0</t>
+          <t>-17,89; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 0,0</t>
+          <t>-18,2; 0,0</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 7,71</t>
+          <t>-10,93; 6,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 0,0</t>
+          <t>-18,29; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 1,96</t>
+          <t>-19,78; 1,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,82; 17,15</t>
+          <t>-13,02; 17,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 3,52</t>
+          <t>-12,37; 2,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 5,85</t>
+          <t>-11,31; 5,72</t>
         </is>
       </c>
     </row>
@@ -878,24 +878,24 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-81,05; 554,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-98,78; 199,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-87,5; 699,32</t>
+          <t>-90,51; 280,6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,44</t>
+          <t>0,0; 23,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,78</t>
+          <t>0,0; 14,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,06</t>
+          <t>0,0; 10,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 0,0</t>
+          <t>-20,21; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 4,77</t>
+          <t>-16,82; 4,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 0,0</t>
+          <t>-9,95; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 2,15</t>
+          <t>-8,72; 1,99</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,9</t>
+          <t>0,0; 19,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,28</t>
+          <t>0,0; 9,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 7,51</t>
+          <t>-9,42; 7,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 9,79</t>
+          <t>-6,28; 9,67</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 9,38</t>
+          <t>-5,2; 9,54</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 0,0</t>
+          <t>-12,35; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 5,86</t>
+          <t>-4,57; 6,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 5,07</t>
+          <t>-5,54; 4,51</t>
         </is>
       </c>
     </row>
@@ -1723,17 +1723,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-19,35; -1,74</t>
+          <t>-19,27; -1,72</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-20,66; -1,75</t>
+          <t>-19,23; -1,72</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,46</t>
+          <t>0,0; 19,77</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 7,19</t>
+          <t>-3,97; 6,9</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,3; -0,68</t>
+          <t>-8,15; -0,69</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 0,45</t>
+          <t>-5,9; 0,48</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 0,06</t>
+          <t>-6,52; -0,37</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,39</t>
+          <t>-2,29; 3,57</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,4</t>
+          <t>-2,8; 2,39</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 1,4</t>
+          <t>-2,91; 1,36</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,33</t>
+          <t>-3,68; 0,22</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-87,28; 40,28</t>
+          <t>-90,45; 37,26</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-91,77; 34,91</t>
+          <t>-92,46; 5,9</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-62,65; 412,25</t>
+          <t>-63,48; 394,01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,91; 312,38</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-65,8; 67,46</t>
+          <t>-65,08; 81,24</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-81,86; 29,26</t>
+          <t>-80,72; 24,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 2,63</t>
+          <t>-25,45; 2,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 2,82</t>
+          <t>-24,24; 3,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 0,0</t>
+          <t>-28,47; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,08; 0,0</t>
+          <t>-30,93; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 0,0</t>
+          <t>-17,06; 0,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 0,0</t>
+          <t>-17,36; 0,27</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 6,56</t>
+          <t>-10,95; 7,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 0,0</t>
+          <t>-18,49; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 1,87</t>
+          <t>-20,79; 3,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 17,78</t>
+          <t>-13,83; 16,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 2,81</t>
+          <t>-12,42; 3,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 5,72</t>
+          <t>-10,86; 6,03</t>
         </is>
       </c>
     </row>
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-81,05; 554,08</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-98,78; 199,21</t>
+          <t>-91,84; 246,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,51; 280,6</t>
+          <t>-89,42; 323,12</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,03</t>
+          <t>0,0; 17,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,6</t>
+          <t>0,0; 13,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,91</t>
+          <t>0,0; 12,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 0,0</t>
+          <t>-20,77; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 4,84</t>
+          <t>-16,63; 4,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 0,0</t>
+          <t>-10,13; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 1,99</t>
+          <t>-8,3; 2,59</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,84</t>
+          <t>0,0; 25,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,94</t>
+          <t>0,0; 11,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 7,72</t>
+          <t>-12,37; 5,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 9,67</t>
+          <t>-6,28; 9,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 9,54</t>
+          <t>-5,2; 9,37</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 0,0</t>
+          <t>-12,39; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 6,77</t>
+          <t>-4,41; 6,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 4,51</t>
+          <t>-5,49; 5,44</t>
         </is>
       </c>
     </row>
@@ -1723,17 +1723,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-19,27; -1,72</t>
+          <t>-18,95; -1,75</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-19,23; -1,72</t>
+          <t>-18,83; -1,74</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,77</t>
+          <t>0,0; 20,7</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 6,9</t>
+          <t>-3,78; 6,56</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-8,15; -0,69</t>
+          <t>-7,92; -0,68</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 0,48</t>
+          <t>-5,82; 0,44</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,52; -0,37</t>
+          <t>-6,33; -0,15</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 3,57</t>
+          <t>-2,25; 3,39</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 2,39</t>
+          <t>-2,73; 2,38</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 1,36</t>
+          <t>-2,85; 1,33</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,22</t>
+          <t>-3,73; 0,34</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-90,45; 37,26</t>
+          <t>-88,98; 41,58</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-92,46; 5,9</t>
+          <t>-92,51; 23,97</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-63,48; 394,01</t>
+          <t>-65,21; 446,31</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-84,91; 312,38</t>
+          <t>-82,4; 329,39</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-65,08; 81,24</t>
+          <t>-66,28; 71,83</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-80,72; 24,51</t>
+          <t>-81,13; 33,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A09-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Provincia-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumieron medicamentos para los vómitos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-5,65</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-5,65</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-6,25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-6,1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-5,65</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 2,71</t>
+          <t>-26,18; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 3,45</t>
+          <t>-29,07; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 0,0</t>
+          <t>-23,42; 2,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,93; 0,0</t>
+          <t>-23,74; 3,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 0,24</t>
+          <t>-18,74; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 0,27</t>
+          <t>-18,89; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-70,49%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-68,84%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-6,44</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,25</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-3,66</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-6,44</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 7,76</t>
+          <t>-21,4; 1,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 0,0</t>
+          <t>-12,82; 17,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 3,2</t>
+          <t>-12,55; 7,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 16,22</t>
+          <t>-18,32; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 3,56</t>
+          <t>-12,28; 3,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 6,03</t>
+          <t>-10,67; 5,85</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-66,04%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23,05%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>5,45%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-66,04%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,84; 246,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,42; 323,12</t>
+          <t>-87,5; 699,32</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>4,08</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,17</t>
+          <t>0,0; 12,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,76</t>
+          <t>0,0; 17,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,34</t>
+          <t>0,0; 11,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-6,4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-3,18</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-20,77; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,57; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-15,93; 4,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 0,0</t>
+          <t>-11,21; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 2,59</t>
+          <t>-8,13; 2,15</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-49,73%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4,76</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,78</t>
+          <t>0,0; 11,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1293,17 +1293,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2,06</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-2,45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-0,28</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,02</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-2,45</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 5,67</t>
+          <t>-5,02; 9,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 9,69</t>
+          <t>-9,99; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 9,37</t>
+          <t>-9,47; 7,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 0,0</t>
+          <t>-6,27; 9,79</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 6,67</t>
+          <t>-4,45; 5,86</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 5,44</t>
+          <t>-5,54; 5,07</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>84,08%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-9,03%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>0,51%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>84,08%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>6,09</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-7,09</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-7,09</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>6,09</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-18,95; -1,75</t>
+          <t>0,0; 18,46</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-18,83; -1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,7</t>
+          <t>-19,35; -1,74</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-20,66; -1,75</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 6,56</t>
+          <t>-3,94; 7,19</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -0,68</t>
+          <t>-7,3; -0,68</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,38</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-2,28</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>-2,75</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,44</t>
+          <t>-2,21; 3,39</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,33; -0,15</t>
+          <t>-3,09; 2,4</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 3,39</t>
+          <t>-5,45; 0,45</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,38</t>
+          <t>-6,23; 0,06</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 1,33</t>
+          <t>-2,98; 1,4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,34</t>
+          <t>-3,62; 0,33</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>28,23%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-16,9%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-54,86%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>-66,23%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-16,9%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-88,98; 41,58</t>
+          <t>-62,65; 412,25</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-92,51; 23,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-65,21; 446,31</t>
+          <t>-87,28; 40,28</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-82,4; 329,39</t>
+          <t>-91,77; 34,91</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-66,28; 71,83</t>
+          <t>-65,8; 67,46</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-81,13; 33,02</t>
+          <t>-81,86; 29,26</t>
         </is>
       </c>
     </row>
